--- a/artfynd/A 39483-2019 artfynd.xlsx
+++ b/artfynd/A 39483-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121558661</v>
+        <v>121558660</v>
       </c>
       <c r="B2" t="n">
         <v>56256</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 39483-2019 artfynd.xlsx
+++ b/artfynd/A 39483-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121558660</v>
+        <v>121558671</v>
       </c>
       <c r="B2" t="n">
-        <v>56256</v>
+        <v>56250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,17 +792,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Johan Eklöf, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning, Johan Eklöf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121558671</v>
+        <v>121558661</v>
       </c>
       <c r="B3" t="n">
-        <v>56249</v>
+        <v>56257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Johan Eklöf, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning, Johan Eklöf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 39483-2019 artfynd.xlsx
+++ b/artfynd/A 39483-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121558671</v>
+        <v>121558660</v>
       </c>
       <c r="B2" t="n">
-        <v>56250</v>
+        <v>56257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,17 +792,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning, Johan Eklöf</t>
+          <t>Alfred Olofsson, Johan Eklöf, Enviro Planning</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121558661</v>
+        <v>121558671</v>
       </c>
       <c r="B3" t="n">
-        <v>56257</v>
+        <v>56250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning, Johan Eklöf</t>
+          <t>Alfred Olofsson, Johan Eklöf, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 39483-2019 artfynd.xlsx
+++ b/artfynd/A 39483-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121558660</v>
+        <v>121558671</v>
       </c>
       <c r="B2" t="n">
-        <v>56257</v>
+        <v>56250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121558671</v>
+        <v>121558660</v>
       </c>
       <c r="B3" t="n">
-        <v>56250</v>
+        <v>56257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 39483-2019 artfynd.xlsx
+++ b/artfynd/A 39483-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121558671</v>
       </c>
       <c r="B2" t="n">
-        <v>56250</v>
+        <v>56251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>121558660</v>
       </c>
       <c r="B3" t="n">
-        <v>56257</v>
+        <v>56258</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 39483-2019 artfynd.xlsx
+++ b/artfynd/A 39483-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121558661</v>
+        <v>121558660</v>
       </c>
       <c r="B2" t="n">
         <v>56258</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 39483-2019 artfynd.xlsx
+++ b/artfynd/A 39483-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121558660</v>
+        <v>121558661</v>
       </c>
       <c r="B2" t="n">
         <v>56258</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 39483-2019 artfynd.xlsx
+++ b/artfynd/A 39483-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121558661</v>
+        <v>121558671</v>
       </c>
       <c r="B2" t="n">
-        <v>56258</v>
+        <v>56251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121558671</v>
+        <v>121558661</v>
       </c>
       <c r="B3" t="n">
-        <v>56251</v>
+        <v>56258</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">

--- a/artfynd/A 39483-2019 artfynd.xlsx
+++ b/artfynd/A 39483-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121558671</v>
+        <v>121558661</v>
       </c>
       <c r="B2" t="n">
-        <v>56251</v>
+        <v>56258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121558661</v>
+        <v>121558671</v>
       </c>
       <c r="B3" t="n">
-        <v>56258</v>
+        <v>56251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">

--- a/artfynd/A 39483-2019 artfynd.xlsx
+++ b/artfynd/A 39483-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121558661</v>
+        <v>121558671</v>
       </c>
       <c r="B2" t="n">
-        <v>56258</v>
+        <v>56251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121558671</v>
+        <v>121558660</v>
       </c>
       <c r="B3" t="n">
-        <v>56251</v>
+        <v>56258</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 39483-2019 artfynd.xlsx
+++ b/artfynd/A 39483-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121558671</v>
+        <v>121558661</v>
       </c>
       <c r="B2" t="n">
-        <v>56251</v>
+        <v>56258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -792,17 +792,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Johan Eklöf, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning, Johan Eklöf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121558660</v>
+        <v>121558671</v>
       </c>
       <c r="B3" t="n">
-        <v>56258</v>
+        <v>56251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +916,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Johan Eklöf, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning, Johan Eklöf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
